--- a/InputData/bldgs/SoDSCbRIC/Shr of Dist Solar Costs by Rcpnt ISIC Code.xlsx
+++ b/InputData/bldgs/SoDSCbRIC/Shr of Dist Solar Costs by Rcpnt ISIC Code.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\bldgs\SoDSCbRIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0318BFB-A884-40BE-884D-423319545896}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE39E34D-69A6-4F3D-B443-E81143DC1E93}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1725" yWindow="435" windowWidth="26295" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="105" windowWidth="25665" windowHeight="16830" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="124">
   <si>
     <t>https://www.nrel.gov/docs/fy19osti/72399.pdf</t>
   </si>
@@ -139,12 +139,6 @@
     <t>Rubber and plastics products</t>
   </si>
   <si>
-    <t>Other non-metallic mineral products</t>
-  </si>
-  <si>
-    <t>Manufacture of basic metals</t>
-  </si>
-  <si>
     <t>Fabricated metal products, except machinery and equipment</t>
   </si>
   <si>
@@ -166,9 +160,6 @@
     <t>Other manufacturing; repair and installation of machinery and equipment</t>
   </si>
   <si>
-    <t>Electricity, gas, water supply, sewerage, waste and remediation services</t>
-  </si>
-  <si>
     <t>Construction</t>
   </si>
   <si>
@@ -244,12 +235,6 @@
     <t>ISIC 22</t>
   </si>
   <si>
-    <t>ISIC 23</t>
-  </si>
-  <si>
-    <t>ISIC 24</t>
-  </si>
-  <si>
     <t>ISIC 25</t>
   </si>
   <si>
@@ -271,9 +256,6 @@
     <t>ISIC 31T33</t>
   </si>
   <si>
-    <t>ISIC 35T39</t>
-  </si>
-  <si>
     <t>ISIC 41T43</t>
   </si>
   <si>
@@ -383,6 +365,48 @@
   </si>
   <si>
     <t>Oil and gas extraction</t>
+  </si>
+  <si>
+    <t>ISIC 231</t>
+  </si>
+  <si>
+    <t>ISIC 239</t>
+  </si>
+  <si>
+    <t>Glass</t>
+  </si>
+  <si>
+    <t>Cement and other nonmetallic minerals</t>
+  </si>
+  <si>
+    <t>ISIC 241</t>
+  </si>
+  <si>
+    <t>ISIC 242</t>
+  </si>
+  <si>
+    <t>Iron and steel</t>
+  </si>
+  <si>
+    <t>Other metals</t>
+  </si>
+  <si>
+    <t>ISIC 351</t>
+  </si>
+  <si>
+    <t>ISIC 352T353</t>
+  </si>
+  <si>
+    <t>ISIC 36T39</t>
+  </si>
+  <si>
+    <t>Electricity generation and distribution</t>
+  </si>
+  <si>
+    <t>Energy pipelines and gas processing</t>
+  </si>
+  <si>
+    <t>Water and waste</t>
   </si>
 </sst>
 </file>
@@ -769,15 +793,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -787,7 +811,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -797,27 +821,27 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -831,7 +855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.7109375" customWidth="1"/>
@@ -854,7 +878,7 @@
         <v>24</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -862,19 +886,19 @@
         <v>23</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H2" t="s">
         <v>25</v>
@@ -896,13 +920,13 @@
         <v>0.11115462948456839</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -921,13 +945,13 @@
         <v>0.10778630737897542</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -946,10 +970,10 @@
         <v>0.11789127369575435</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H5" t="s">
         <v>26</v>
@@ -971,10 +995,10 @@
         <v>2.020993263355789E-2</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H6" t="s">
         <v>27</v>
@@ -996,10 +1020,10 @@
         <v>9.0944696851010504E-2</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s">
         <v>28</v>
@@ -1020,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H8" t="s">
         <v>29</v>
@@ -1042,10 +1066,10 @@
         <v>0.12454958483471723</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H9" t="s">
         <v>30</v>
@@ -1067,10 +1091,10 @@
         <v>9.4234685884380387E-2</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H10" t="s">
         <v>31</v>
@@ -1092,10 +1116,10 @@
         <v>5.7183142722857593E-2</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H11" t="s">
         <v>32</v>
@@ -1117,13 +1141,13 @@
         <v>9.4234685884380387E-2</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G12" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H12" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1142,18 +1166,18 @@
         <v>0.1818110606297979</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H14" t="s">
         <v>33</v>
@@ -1168,10 +1192,10 @@
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="G15" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="H15" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -1179,22 +1203,22 @@
         <v>22</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="H16" t="s">
-        <v>35</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1213,13 +1237,13 @@
         <v>5.9203313436472164E-2</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="H17" t="s">
-        <v>36</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1238,13 +1262,13 @@
         <v>2.4668047265196738E-2</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="H18" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,13 +1287,13 @@
         <v>0.17760994030941649</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1287,10 +1311,10 @@
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H20" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1309,13 +1333,13 @@
         <v>4.9336094530393476E-2</v>
       </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G21" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H21" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1334,13 +1358,13 @@
         <v>8.8804970154708243E-2</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G22" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H22" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1359,13 +1383,13 @@
         <v>7.8937751248629548E-2</v>
       </c>
       <c r="E23" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G23" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1384,13 +1408,13 @@
         <v>9.9524911682299919E-2</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G24" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H24" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1409,13 +1433,13 @@
         <v>8.9657692776221209E-2</v>
       </c>
       <c r="E25" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G25" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1434,13 +1458,13 @@
         <v>6.9923254964063833E-2</v>
       </c>
       <c r="E26" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G26" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="H26" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1459,109 +1483,141 @@
         <v>0.26233402363259839</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G27" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="H27" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G28" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="H28" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G29" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H29" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G30" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="H30" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G31" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G32" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H32" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G33" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H33" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G34" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G35" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G36" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G37" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G38" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G39" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s">
-        <v>59</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G40" t="s">
+        <v>84</v>
+      </c>
+      <c r="H40" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G41" t="s">
+        <v>85</v>
+      </c>
+      <c r="H41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G42" t="s">
+        <v>86</v>
+      </c>
+      <c r="H42" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G43" t="s">
+        <v>55</v>
+      </c>
+      <c r="H43" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1574,131 +1630,143 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AM4"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B1" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="L1" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="N1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="O1" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="S1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="T1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="L1" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="N1" s="10" t="s">
+      <c r="U1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="V1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="W1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="X1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="Y1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="Z1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA1" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB1" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="AD1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="AE1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="AF1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="AG1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="AH1" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="AI1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="AJ1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AK1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AL1" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AM1" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AN1" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="AE1" s="10" t="s">
+      <c r="AO1" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="AF1" s="10" t="s">
+      <c r="AP1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="AG1" s="10" t="s">
+      <c r="AQ1" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>87</v>
-      </c>
-      <c r="AH1" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI1" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="AJ1" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="AK1" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL1" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM1" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>93</v>
       </c>
       <c r="B2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!B1,Data!$D$3:$D$13)</f>
@@ -1762,23 +1830,23 @@
       </c>
       <c r="Q2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!Q1,Data!$D$3:$D$13)</f>
-        <v>5.7183142722857593E-2</v>
+        <v>0</v>
       </c>
       <c r="R2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!R1,Data!$D$3:$D$13)</f>
-        <v>0.1818110606297979</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!S1,Data!$D$3:$D$13)</f>
-        <v>0.18846937176876077</v>
+        <v>5.7183142722857593E-2</v>
       </c>
       <c r="T2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!T1,Data!$D$3:$D$13)</f>
-        <v>0</v>
+        <v>0.1818110606297979</v>
       </c>
       <c r="U2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!U1,Data!$D$3:$D$13)</f>
-        <v>0</v>
+        <v>0.18846937176876077</v>
       </c>
       <c r="V2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!V1,Data!$D$3:$D$13)</f>
@@ -1794,7 +1862,7 @@
       </c>
       <c r="Y2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!Y1,Data!$D$3:$D$13)</f>
-        <v>0.30988563371455435</v>
+        <v>0</v>
       </c>
       <c r="Z2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!Z1,Data!$D$3:$D$13)</f>
@@ -1802,7 +1870,7 @@
       </c>
       <c r="AA2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AA1,Data!$D$3:$D$13)</f>
-        <v>0.12454958483471723</v>
+        <v>0</v>
       </c>
       <c r="AB2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AB1,Data!$D$3:$D$13)</f>
@@ -1810,7 +1878,7 @@
       </c>
       <c r="AC2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AC1,Data!$D$3:$D$13)</f>
-        <v>0</v>
+        <v>0.30988563371455435</v>
       </c>
       <c r="AD2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AD1,Data!$D$3:$D$13)</f>
@@ -1818,7 +1886,7 @@
       </c>
       <c r="AE2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AE1,Data!$D$3:$D$13)</f>
-        <v>0</v>
+        <v>0.12454958483471723</v>
       </c>
       <c r="AF2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AF1,Data!$D$3:$D$13)</f>
@@ -1830,7 +1898,7 @@
       </c>
       <c r="AH2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AH1,Data!$D$3:$D$13)</f>
-        <v>0.13810120632931225</v>
+        <v>0</v>
       </c>
       <c r="AI2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AI1,Data!$D$3:$D$13)</f>
@@ -1846,23 +1914,39 @@
       </c>
       <c r="AL2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AL1,Data!$D$3:$D$13)</f>
-        <v>0</v>
+        <v>0.13810120632931225</v>
       </c>
       <c r="AM2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AM1,Data!$D$3:$D$13)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN2">
+        <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AN1,Data!$D$3:$D$13)</f>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AO1,Data!$D$3:$D$13)</f>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AP1,Data!$D$3:$D$13)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!AQ1,Data!$D$3:$D$13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B3">
         <f>B2</f>
         <v>0</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:AM3" si="0">C2</f>
+        <f t="shared" ref="C3:AQ3" si="0">C2</f>
         <v>0</v>
       </c>
       <c r="D3">
@@ -1914,29 +1998,29 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="P3" si="3">P2</f>
         <v>0</v>
       </c>
       <c r="Q3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3" si="4">R2</f>
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <f t="shared" si="0"/>
         <v>5.7183142722857593E-2</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <f t="shared" si="0"/>
         <v>0.1818110606297979</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <f t="shared" si="0"/>
         <v>0.18846937176876077</v>
       </c>
-      <c r="T3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="V3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1951,32 +2035,32 @@
       </c>
       <c r="Y3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" ref="AA3:AB3" si="5">AA2</f>
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <f t="shared" si="0"/>
         <v>0.30988563371455435</v>
       </c>
-      <c r="Z3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA3">
+      <c r="AD3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE3">
         <f t="shared" si="0"/>
         <v>0.12454958483471723</v>
       </c>
-      <c r="AB3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="AF3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1987,32 +2071,48 @@
       </c>
       <c r="AH3">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="0"/>
         <v>0.13810120632931225</v>
       </c>
-      <c r="AI3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="AM3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!B1,Data!$D$17:$D$27)</f>
@@ -2076,23 +2176,23 @@
       </c>
       <c r="Q4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!Q1,Data!$D$17:$D$27)</f>
-        <v>8.9657692776221209E-2</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!R1,Data!$D$17:$D$27)</f>
-        <v>0.26233402363259839</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!S1,Data!$D$17:$D$27)</f>
-        <v>0.16944816664636375</v>
+        <v>8.9657692776221209E-2</v>
       </c>
       <c r="T4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!T1,Data!$D$17:$D$27)</f>
-        <v>0</v>
+        <v>0.26233402363259839</v>
       </c>
       <c r="U4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!U1,Data!$D$17:$D$27)</f>
-        <v>0</v>
+        <v>0.16944816664636375</v>
       </c>
       <c r="V4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!V1,Data!$D$17:$D$27)</f>
@@ -2108,7 +2208,7 @@
       </c>
       <c r="Y4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!Y1,Data!$D$17:$D$27)</f>
-        <v>0.42922402241442315</v>
+        <v>0</v>
       </c>
       <c r="Z4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!Z1,Data!$D$17:$D$27)</f>
@@ -2124,7 +2224,7 @@
       </c>
       <c r="AC4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!AC1,Data!$D$17:$D$27)</f>
-        <v>0</v>
+        <v>0.42922402241442315</v>
       </c>
       <c r="AD4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!AD1,Data!$D$17:$D$27)</f>
@@ -2144,7 +2244,7 @@
       </c>
       <c r="AH4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!AH1,Data!$D$17:$D$27)</f>
-        <v>4.9336094530393476E-2</v>
+        <v>0</v>
       </c>
       <c r="AI4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!AI1,Data!$D$17:$D$27)</f>
@@ -2160,10 +2260,26 @@
       </c>
       <c r="AL4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!AL1,Data!$D$17:$D$27)</f>
-        <v>0</v>
+        <v>4.9336094530393476E-2</v>
       </c>
       <c r="AM4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!AM1,Data!$D$17:$D$27)</f>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!AN1,Data!$D$17:$D$27)</f>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!AO1,Data!$D$17:$D$27)</f>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!AP1,Data!$D$17:$D$27)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!AQ1,Data!$D$17:$D$27)</f>
         <v>0</v>
       </c>
     </row>

--- a/InputData/bldgs/SoDSCbRIC/Shr of Dist Solar Costs by Rcpnt ISIC Code.xlsx
+++ b/InputData/bldgs/SoDSCbRIC/Shr of Dist Solar Costs by Rcpnt ISIC Code.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27706"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\bldgs\SoDSCbRIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE39E34D-69A6-4F3D-B443-E81143DC1E93}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE39E34D-69A6-4F3D-B443-E81143DC1E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3105" yWindow="105" windowWidth="25665" windowHeight="16830" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="105" windowWidth="25665" windowHeight="16830" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
     <sheet name="Data" sheetId="1" r:id="rId2"/>
     <sheet name="SoDSCbRIC" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,168 +40,360 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="124">
   <si>
+    <t>SoDSCbRIC Share of Distriuted Solar Costs by Recipient ISIC Code</t>
+  </si>
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>NREL</t>
+  </si>
+  <si>
+    <t>U.S. Solar Photovoltaic System Cost Benchmark: Q1 2018</t>
+  </si>
+  <si>
     <t>https://www.nrel.gov/docs/fy19osti/72399.pdf</t>
   </si>
   <si>
+    <t>Figures 14 and 20</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>As taxes (except fuel taxes) are handled separately (on the "Cross-Sector Totals" sheet), not within</t>
+  </si>
+  <si>
+    <t>each sector, we reallocate the "sales tax" share in this variable to the equipment portions</t>
+  </si>
+  <si>
+    <t>of the costs.</t>
+  </si>
+  <si>
     <t>Residential</t>
   </si>
   <si>
+    <t>ISIC Code</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>2018 USD/W-DC, mixed weighted average, 6.2 kW</t>
+  </si>
+  <si>
+    <t>Pre-Tax Reallocation</t>
+  </si>
+  <si>
+    <t>Share</t>
+  </si>
+  <si>
+    <t>ISIC 01T03</t>
+  </si>
+  <si>
+    <t>Agriculture, forestry and fishing</t>
+  </si>
+  <si>
     <t>Net Profit</t>
   </si>
   <si>
+    <t>ISIC 41T43</t>
+  </si>
+  <si>
+    <t>ISIC 05</t>
+  </si>
+  <si>
+    <t>Coal mining</t>
+  </si>
+  <si>
     <t>Overhead</t>
   </si>
   <si>
+    <t>ISIC 06</t>
+  </si>
+  <si>
+    <t>Oil and gas extraction</t>
+  </si>
+  <si>
     <t>Sales and Marketing</t>
   </si>
   <si>
+    <t>ISIC 69T82</t>
+  </si>
+  <si>
+    <t>ISIC 07T08</t>
+  </si>
+  <si>
+    <t>Mining and quarrying of non-energy producing products</t>
+  </si>
+  <si>
     <t>Permitting, Inspection, Interconnection</t>
   </si>
   <si>
+    <t>ISIC 09</t>
+  </si>
+  <si>
+    <t>Mining support service activities</t>
+  </si>
+  <si>
     <t>Install Labor</t>
   </si>
   <si>
+    <t>ISIC 10T12</t>
+  </si>
+  <si>
+    <t>Food products, beverages and tobacco</t>
+  </si>
+  <si>
     <t>Sales Tax</t>
   </si>
   <si>
+    <t>ISIC 13T15</t>
+  </si>
+  <si>
+    <t>Textiles, wearing apparel, leather and related products</t>
+  </si>
+  <si>
     <t>Supply Chain Costs</t>
   </si>
   <si>
+    <t>ISIC 49T53</t>
+  </si>
+  <si>
+    <t>ISIC 16</t>
+  </si>
+  <si>
+    <t>Wood and of products of wood and cork (except furniture)</t>
+  </si>
+  <si>
     <t>Electrical BOS</t>
   </si>
   <si>
+    <t>ISIC 27</t>
+  </si>
+  <si>
+    <t>ISIC 17T18</t>
+  </si>
+  <si>
+    <t>Paper products and printing</t>
+  </si>
+  <si>
     <t>Structrual BOS</t>
   </si>
   <si>
+    <t>ISIC 25</t>
+  </si>
+  <si>
+    <t>ISIC 19</t>
+  </si>
+  <si>
+    <t>Coke and refined petroleum products</t>
+  </si>
+  <si>
     <t>Inverter</t>
   </si>
   <si>
+    <t>ISIC 20</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
     <t>Module</t>
   </si>
   <si>
+    <t>ISIC 26</t>
+  </si>
+  <si>
+    <t>ISIC 21</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>ISIC 22</t>
+  </si>
+  <si>
+    <t>Rubber and plastics products</t>
+  </si>
+  <si>
     <t>Commercial</t>
   </si>
   <si>
+    <t>ISIC 231</t>
+  </si>
+  <si>
+    <t>Glass</t>
+  </si>
+  <si>
+    <t>2018 USD/W-DC, 200 kW</t>
+  </si>
+  <si>
+    <t>ISIC 239</t>
+  </si>
+  <si>
+    <t>Cement and other nonmetallic minerals</t>
+  </si>
+  <si>
     <t>EPC/Developer Net Profit</t>
   </si>
   <si>
+    <t>ISIC 241</t>
+  </si>
+  <si>
+    <t>Iron and steel</t>
+  </si>
+  <si>
     <t>Contingency</t>
   </si>
   <si>
+    <t>ISIC 242</t>
+  </si>
+  <si>
+    <t>Other metals</t>
+  </si>
+  <si>
     <t>Developer Overhead</t>
   </si>
   <si>
+    <t>Fabricated metal products, except machinery and equipment</t>
+  </si>
+  <si>
+    <t>Computer, electronic and optical products</t>
+  </si>
+  <si>
     <t>PII</t>
   </si>
   <si>
+    <t>Electrical equipment</t>
+  </si>
+  <si>
     <t>EPC Overhead</t>
   </si>
   <si>
+    <t>ISIC 28</t>
+  </si>
+  <si>
+    <t>Machinery and equipment n.e.c.</t>
+  </si>
+  <si>
     <t>Install Labor and Equipment</t>
   </si>
   <si>
+    <t>ISIC 29</t>
+  </si>
+  <si>
+    <t>Motor vehicles, trailers and semi-trailers</t>
+  </si>
+  <si>
+    <t>ISIC 30</t>
+  </si>
+  <si>
+    <t>Other transport equipment</t>
+  </si>
+  <si>
     <t>Structural BOS</t>
   </si>
   <si>
+    <t>ISIC 31T33</t>
+  </si>
+  <si>
+    <t>Other manufacturing; repair and installation of machinery and equipment</t>
+  </si>
+  <si>
     <t>Inverter Only</t>
   </si>
   <si>
-    <t>2018 USD/W-DC, 200 kW</t>
-  </si>
-  <si>
-    <t>2018 USD/W-DC, mixed weighted average, 6.2 kW</t>
-  </si>
-  <si>
-    <t>ISIC Code</t>
-  </si>
-  <si>
-    <t>Agriculture, forestry and fishing</t>
-  </si>
-  <si>
-    <t>Mining and quarrying of non-energy producing products</t>
-  </si>
-  <si>
-    <t>Mining support service activities</t>
-  </si>
-  <si>
-    <t>Food products, beverages and tobacco</t>
-  </si>
-  <si>
-    <t>Textiles, wearing apparel, leather and related products</t>
-  </si>
-  <si>
-    <t>Wood and of products of wood and cork (except furniture)</t>
-  </si>
-  <si>
-    <t>Paper products and printing</t>
-  </si>
-  <si>
-    <t>Coke and refined petroleum products</t>
-  </si>
-  <si>
-    <t>Rubber and plastics products</t>
-  </si>
-  <si>
-    <t>Fabricated metal products, except machinery and equipment</t>
-  </si>
-  <si>
-    <t>Computer, electronic and optical products</t>
-  </si>
-  <si>
-    <t>Electrical equipment</t>
-  </si>
-  <si>
-    <t>Machinery and equipment n.e.c.</t>
-  </si>
-  <si>
-    <t>Motor vehicles, trailers and semi-trailers</t>
-  </si>
-  <si>
-    <t>Other transport equipment</t>
-  </si>
-  <si>
-    <t>Other manufacturing; repair and installation of machinery and equipment</t>
+    <t>ISIC 351</t>
+  </si>
+  <si>
+    <t>Electricity generation and distribution</t>
+  </si>
+  <si>
+    <t>ISIC 352T353</t>
+  </si>
+  <si>
+    <t>Energy pipelines and gas processing</t>
+  </si>
+  <si>
+    <t>ISIC 36T39</t>
+  </si>
+  <si>
+    <t>Water and waste</t>
   </si>
   <si>
     <t>Construction</t>
   </si>
   <si>
+    <t>ISIC 45T47</t>
+  </si>
+  <si>
     <t>Wholesale and retail trade; repair of motor vehicles</t>
   </si>
   <si>
     <t>Transportation and storage</t>
   </si>
   <si>
+    <t>ISIC 55T56</t>
+  </si>
+  <si>
     <t>Accomodation and food services</t>
   </si>
   <si>
+    <t>ISIC 58T60</t>
+  </si>
+  <si>
     <t>Publishing, audiovisual and broadcasting activities</t>
   </si>
   <si>
+    <t>ISIC 61</t>
+  </si>
+  <si>
     <t>Telecommunications</t>
   </si>
   <si>
+    <t>ISIC 62T63</t>
+  </si>
+  <si>
     <t>IT and other information services</t>
   </si>
   <si>
+    <t>ISIC 64T66</t>
+  </si>
+  <si>
     <t>Financial and insurance activities</t>
   </si>
   <si>
+    <t>ISIC 68</t>
+  </si>
+  <si>
     <t>Real estate activities</t>
   </si>
   <si>
     <t>Other business sector services</t>
   </si>
   <si>
+    <t>ISIC 84</t>
+  </si>
+  <si>
     <t>Public administration and defence; compulsory social security</t>
   </si>
   <si>
+    <t>ISIC 85</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
+    <t>ISIC 86T88</t>
+  </si>
+  <si>
     <t>Human health and social work</t>
   </si>
   <si>
+    <t>ISIC 90T96</t>
+  </si>
+  <si>
     <t>Arts, entertainment, recreation and other service activities</t>
   </si>
   <si>
@@ -208,96 +403,6 @@
     <t>Private households with employed persons</t>
   </si>
   <si>
-    <t>ISIC 01T03</t>
-  </si>
-  <si>
-    <t>ISIC 07T08</t>
-  </si>
-  <si>
-    <t>ISIC 09</t>
-  </si>
-  <si>
-    <t>ISIC 10T12</t>
-  </si>
-  <si>
-    <t>ISIC 13T15</t>
-  </si>
-  <si>
-    <t>ISIC 16</t>
-  </si>
-  <si>
-    <t>ISIC 17T18</t>
-  </si>
-  <si>
-    <t>ISIC 19</t>
-  </si>
-  <si>
-    <t>ISIC 22</t>
-  </si>
-  <si>
-    <t>ISIC 25</t>
-  </si>
-  <si>
-    <t>ISIC 26</t>
-  </si>
-  <si>
-    <t>ISIC 27</t>
-  </si>
-  <si>
-    <t>ISIC 28</t>
-  </si>
-  <si>
-    <t>ISIC 29</t>
-  </si>
-  <si>
-    <t>ISIC 30</t>
-  </si>
-  <si>
-    <t>ISIC 31T33</t>
-  </si>
-  <si>
-    <t>ISIC 41T43</t>
-  </si>
-  <si>
-    <t>ISIC 45T47</t>
-  </si>
-  <si>
-    <t>ISIC 49T53</t>
-  </si>
-  <si>
-    <t>ISIC 55T56</t>
-  </si>
-  <si>
-    <t>ISIC 58T60</t>
-  </si>
-  <si>
-    <t>ISIC 61</t>
-  </si>
-  <si>
-    <t>ISIC 62T63</t>
-  </si>
-  <si>
-    <t>ISIC 64T66</t>
-  </si>
-  <si>
-    <t>ISIC 68</t>
-  </si>
-  <si>
-    <t>ISIC 69T82</t>
-  </si>
-  <si>
-    <t>ISIC 84</t>
-  </si>
-  <si>
-    <t>ISIC 85</t>
-  </si>
-  <si>
-    <t>ISIC 86T88</t>
-  </si>
-  <si>
-    <t>ISIC 90T96</t>
-  </si>
-  <si>
     <t>urban residential</t>
   </si>
   <si>
@@ -305,115 +410,13 @@
   </si>
   <si>
     <t>commercial</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>NREL</t>
-  </si>
-  <si>
-    <t>U.S. Solar Photovoltaic System Cost Benchmark: Q1 2018</t>
-  </si>
-  <si>
-    <t>Figures 14 and 20</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>As taxes (except fuel taxes) are handled separately (on the "Cross-Sector Totals" sheet), not within</t>
-  </si>
-  <si>
-    <t>each sector, we reallocate the "sales tax" share in this variable to the equipment portions</t>
-  </si>
-  <si>
-    <t>of the costs.</t>
-  </si>
-  <si>
-    <t>Share</t>
-  </si>
-  <si>
-    <t>Pre-Tax Reallocation</t>
-  </si>
-  <si>
-    <t>Meaning</t>
-  </si>
-  <si>
-    <t>SoDSCbRIC Share of Distriuted Solar Costs by Recipient ISIC Code</t>
-  </si>
-  <si>
-    <t>ISIC 20</t>
-  </si>
-  <si>
-    <t>ISIC 21</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>ISIC 05</t>
-  </si>
-  <si>
-    <t>ISIC 06</t>
-  </si>
-  <si>
-    <t>Coal mining</t>
-  </si>
-  <si>
-    <t>Oil and gas extraction</t>
-  </si>
-  <si>
-    <t>ISIC 231</t>
-  </si>
-  <si>
-    <t>ISIC 239</t>
-  </si>
-  <si>
-    <t>Glass</t>
-  </si>
-  <si>
-    <t>Cement and other nonmetallic minerals</t>
-  </si>
-  <si>
-    <t>ISIC 241</t>
-  </si>
-  <si>
-    <t>ISIC 242</t>
-  </si>
-  <si>
-    <t>Iron and steel</t>
-  </si>
-  <si>
-    <t>Other metals</t>
-  </si>
-  <si>
-    <t>ISIC 351</t>
-  </si>
-  <si>
-    <t>ISIC 352T353</t>
-  </si>
-  <si>
-    <t>ISIC 36T39</t>
-  </si>
-  <si>
-    <t>Electricity generation and distribution</t>
-  </si>
-  <si>
-    <t>Energy pipelines and gas processing</t>
-  </si>
-  <si>
-    <t>Water and waste</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -786,62 +789,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="51.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" s="3">
         <v>2018</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="B6" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -856,7 +859,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="39.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
@@ -866,47 +869,47 @@
     <col min="8" max="8" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="7" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
       <c r="G1" s="7" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="30">
       <c r="A2" s="9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>0.33</v>
@@ -920,18 +923,18 @@
         <v>0.11115462948456839</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0.32</v>
@@ -945,18 +948,18 @@
         <v>0.10778630737897542</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>0.35</v>
@@ -970,18 +973,18 @@
         <v>0.11789127369575435</v>
       </c>
       <c r="E5" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>0.06</v>
@@ -995,18 +998,18 @@
         <v>2.020993263355789E-2</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>0.27</v>
@@ -1020,18 +1023,18 @@
         <v>9.0944696851010504E-2</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>0.09</v>
@@ -1044,15 +1047,15 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B9">
         <v>0.3</v>
@@ -1066,18 +1069,18 @@
         <v>0.12454958483471723</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>0.21</v>
@@ -1091,18 +1094,18 @@
         <v>9.4234685884380387E-2</v>
       </c>
       <c r="E10" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>0.1</v>
@@ -1116,18 +1119,18 @@
         <v>5.7183142722857593E-2</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="B12">
         <v>0.21</v>
@@ -1141,18 +1144,18 @@
         <v>9.4234685884380387E-2</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="G12" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="H12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="B13">
         <v>0.47</v>
@@ -1166,64 +1169,64 @@
         <v>0.1818110606297979</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="G13" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="G14" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="7" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="G15" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="30">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="H16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="B17">
         <v>0.12</v>
@@ -1237,18 +1240,18 @@
         <v>5.9203313436472164E-2</v>
       </c>
       <c r="E17" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="G17" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="B18">
         <v>0.05</v>
@@ -1262,18 +1265,18 @@
         <v>2.4668047265196738E-2</v>
       </c>
       <c r="E18" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="G18" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="H18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="B19">
         <v>0.36</v>
@@ -1287,18 +1290,18 @@
         <v>0.17760994030941649</v>
       </c>
       <c r="E19" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="H19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B20">
         <v>0.05</v>
@@ -1311,15 +1314,15 @@
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="H20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="B21">
         <v>0.1</v>
@@ -1333,18 +1336,18 @@
         <v>4.9336094530393476E-2</v>
       </c>
       <c r="E21" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="B22">
         <v>0.18</v>
@@ -1358,18 +1361,18 @@
         <v>8.8804970154708243E-2</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="G22" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="B23">
         <v>0.16</v>
@@ -1383,18 +1386,18 @@
         <v>7.8937751248629548E-2</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B24">
         <v>0.14000000000000001</v>
@@ -1408,18 +1411,18 @@
         <v>9.9524911682299919E-2</v>
       </c>
       <c r="E24" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="G24" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="B25">
         <v>0.12</v>
@@ -1433,18 +1436,18 @@
         <v>8.9657692776221209E-2</v>
       </c>
       <c r="E25" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G25" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="H25" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="B26">
         <v>0.08</v>
@@ -1458,18 +1461,18 @@
         <v>6.9923254964063833E-2</v>
       </c>
       <c r="E26" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="G26" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="B27">
         <v>0.47</v>
@@ -1483,141 +1486,141 @@
         <v>0.26233402363259839</v>
       </c>
       <c r="E27" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="G27" t="s">
+        <v>90</v>
+      </c>
+      <c r="H27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="G28" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="G30" t="s">
+        <v>95</v>
+      </c>
+      <c r="H30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="G31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H31" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="G32" t="s">
+        <v>98</v>
+      </c>
+      <c r="H32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="7:8">
+      <c r="G33" t="s">
+        <v>100</v>
+      </c>
+      <c r="H33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="7:8">
+      <c r="G34" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="7:8">
+      <c r="G35" t="s">
+        <v>104</v>
+      </c>
+      <c r="H35" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="7:8">
+      <c r="G36" t="s">
+        <v>106</v>
+      </c>
+      <c r="H36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="7:8">
+      <c r="G37" t="s">
+        <v>108</v>
+      </c>
+      <c r="H37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="7:8">
+      <c r="G38" t="s">
+        <v>26</v>
+      </c>
+      <c r="H38" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="7:8">
+      <c r="G39" t="s">
+        <v>111</v>
+      </c>
+      <c r="H39" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" spans="7:8">
+      <c r="G40" t="s">
+        <v>113</v>
+      </c>
+      <c r="H40" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="7:8">
+      <c r="G41" t="s">
+        <v>115</v>
+      </c>
+      <c r="H41" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="7:8">
+      <c r="G42" t="s">
+        <v>117</v>
+      </c>
+      <c r="H42" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="7:8">
+      <c r="G43" t="s">
         <v>119</v>
       </c>
-      <c r="H27" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G28" t="s">
+      <c r="H43" t="s">
         <v>120</v>
-      </c>
-      <c r="H28" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H29" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G30" t="s">
-        <v>74</v>
-      </c>
-      <c r="H30" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G31" t="s">
-        <v>75</v>
-      </c>
-      <c r="H31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G32" t="s">
-        <v>76</v>
-      </c>
-      <c r="H32" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G33" t="s">
-        <v>77</v>
-      </c>
-      <c r="H33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G34" t="s">
-        <v>78</v>
-      </c>
-      <c r="H34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G35" t="s">
-        <v>79</v>
-      </c>
-      <c r="H35" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G36" t="s">
-        <v>80</v>
-      </c>
-      <c r="H36" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G37" t="s">
-        <v>81</v>
-      </c>
-      <c r="H37" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G38" t="s">
-        <v>82</v>
-      </c>
-      <c r="H38" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G39" t="s">
-        <v>83</v>
-      </c>
-      <c r="H39" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="40" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G40" t="s">
-        <v>84</v>
-      </c>
-      <c r="H40" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G41" t="s">
-        <v>85</v>
-      </c>
-      <c r="H41" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G42" t="s">
-        <v>86</v>
-      </c>
-      <c r="H42" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G43" t="s">
-        <v>55</v>
-      </c>
-      <c r="H43" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1631,142 +1634,142 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AQ4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43">
       <c r="B1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="O1" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="S1" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="U1" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="V1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="X1" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z1" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD1" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF1" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG1" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH1" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="AI1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ1" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="P1" s="10" t="s">
+      <c r="AK1" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM1" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="Q1" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="R1" s="10" t="s">
+      <c r="AN1" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO1" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="S1" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="U1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="V1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="W1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="X1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z1" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AP1" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="AQ1" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="AB1" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="AC1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AG1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL1" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="AM1" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN1" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AO1" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AP1" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AQ1" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:43">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="B2">
         <f>SUMIF(Data!$E$3:$E$13,SoDSCbRIC!B1,Data!$D$3:$D$13)</f>
@@ -1937,9 +1940,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="B3">
         <f>B2</f>
@@ -2110,9 +2113,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="B4">
         <f>SUMIF(Data!$E$17:$E$27,SoDSCbRIC!B1,Data!$D$17:$D$27)</f>
@@ -2286,4 +2289,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{126CF305-ECE7-4659-AAFE-A694FF15A1B9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E290F7-A13E-4117-86FC-9717DE3B65CA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57AE9868-02D4-4B42-90A3-6A06D8768064}"/>
 </file>